--- a/aq_files/0473.xlsx
+++ b/aq_files/0473.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Types of Data Sources" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,783 +413,458 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>Option A</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Option B</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Option C</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Option D</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Correct Answer</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Difficulty</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Which of the following is a structured data source?</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Relational database</t>
+          <t>Like_Limit_Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Images</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Videos</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Logs</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>A company wants to generate a detailed employee report. Write a SQL query using Like Limit Group By to retrieve all employee details along with department names.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Which is an unstructured data source?</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Text files</t>
+          <t>Like_Limit_Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Spreadsheets</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>SQL DB</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Write a query using Like Limit Group By to retrieve distinct department IDs from Employees table.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>API is a type of:</t>
-        </is>
+      <c r="A4" t="n">
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Data source</t>
+          <t>Like_Limit_Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UI tool</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Database</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Language</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>A manager wants to display employee names as 'Employee Name'. Write a query using Like Limit Group By with aliases.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Sensor data is considered:</t>
-        </is>
+      <c r="A5" t="n">
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Streaming data</t>
+          <t>Like_Limit_Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Static data</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Manual data</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Write a query using Like Limit Group By to find employees whose salary is greater than 50000 and belong to dept_id = 1.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Which is semi-structured data?</t>
-        </is>
+      <c r="A6" t="n">
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>Like_Limit_Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Images</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Audio</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Using Like Limit Group By, retrieve employees whose salary lies between 40000 and 70000.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Data sources provide:</t>
-        </is>
+      <c r="A7" t="n">
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Raw data</t>
+          <t>Like_Limit_Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Testing</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Write a query using Like Limit Group By to display employees sorted by salary in descending order.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Which is batch data source?</t>
-        </is>
+      <c r="A8" t="n">
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Logs</t>
+          <t>Like_Limit_Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Live streams</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sensors</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>APIs</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Using Like Limit Group By, retrieve employees whose department is in (1,2,3).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Streaming data source example:</t>
-        </is>
+      <c r="A9" t="n">
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IoT sensors</t>
+          <t>Like_Limit_Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Excel file</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Word</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Write a query using Like Limit Group By to find employees whose names start with 'A'.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Internal data source means:</t>
-        </is>
+      <c r="A10" t="n">
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Within organization</t>
+          <t>Like_Limit_Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>External APIs</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Public data</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Using Like Limit Group By, limit the output to top 5 highest paid employees.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>External data source example:</t>
-        </is>
+      <c r="A11" t="n">
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Third-party API</t>
+          <t>Like_Limit_Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Internal DB</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Logs</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Files</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Write a query using Like Limit Group By to find employees with NULL manager_id.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Why multiple sources used?</t>
-        </is>
+      <c r="A12" t="n">
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Data variety</t>
+          <t>Like_Limit_Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Testing</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Using Like Limit Group By, group employees by department and calculate average salary.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Which is real-time source?</t>
-        </is>
+      <c r="A13" t="n">
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kafka stream</t>
+          <t>Like_Limit_Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CSV file</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Excel</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Write a query using Like Limit Group By to find departments having more than 3 employees.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Data source reliability affects:</t>
-        </is>
+      <c r="A14" t="n">
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Like_Limit_Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Fonts</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Using Like Limit Group By, find employees whose salary is greater than average salary using subquery.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Data ingestion depends on:</t>
-        </is>
+      <c r="A15" t="n">
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Source type</t>
+          <t>Like_Limit_Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Testing</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Write a query using Like Limit Group By to find employees working in departments with highest salary.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Scenario: social media data → type?</t>
-        </is>
+      <c r="A16" t="n">
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Unstructured</t>
+          <t>Like_Limit_Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Structured</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Tables</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Using Like Limit Group By, retrieve employees who are not assigned to any project.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Scenario: financial records → type?</t>
-        </is>
+      <c r="A17" t="n">
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Structured</t>
+          <t>Like_Limit_Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Unstructured</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Images</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Write a query using Like Limit Group By to calculate total hours worked per employee.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Scenario: API failure → impact?</t>
-        </is>
+      <c r="A18" t="n">
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Data loss</t>
+          <t>Like_Limit_Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UI issue</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Design issue</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Using Like Limit Group By, find employees whose salary is within top 10% in company.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Why validate sources?</t>
-        </is>
+      <c r="A19" t="n">
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ensure accuracy</t>
+          <t>Like_Limit_Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Testing</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Write a query using Like Limit Group By to list departments with total salary greater than 200000.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Multiple formats require:</t>
-        </is>
+      <c r="A20" t="n">
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Flexible pipelines</t>
+          <t>Like_Limit_Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Testing</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Using Like Limit Group By, find employees working on multiple projects.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Source latency affects:</t>
-        </is>
+      <c r="A21" t="n">
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pipeline speed</t>
+          <t>Like_Limit_Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Testing</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Write a query using Like Limit Group By to retrieve employees along with department and project details.</t>
         </is>
       </c>
     </row>
